--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -2142,10 +2142,145 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="0" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C83" t="inlineStr">
         <is>
           <t>-0.325%</t>
         </is>
@@ -2163,7 +2298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3272,10 +3407,145 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="0" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C83" t="inlineStr">
         <is>
           <t>-0.325%</t>
         </is>
@@ -3293,7 +3563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -4149,10 +4419,145 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="0" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>-3.0281%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>-3.0281%</t>
         </is>
@@ -4169,7 +4574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5025,10 +5430,145 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="0" t="n">
         <v>0.99244</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>-3.4901%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.99244</v>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>-3.4901%</t>
         </is>
@@ -5046,7 +5586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5092,10 +5632,145 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="0" t="n">
         <v>1.00005</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5112,7 +5787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5158,10 +5833,145 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="0" t="n">
         <v>1.00005</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.00005</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>

--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -2142,145 +2142,10 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C78" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C79" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B81" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C81" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C82" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C83" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>-0.325%</t>
         </is>
@@ -2298,7 +2163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3407,145 +3272,10 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C78" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C79" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B81" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C81" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C82" s="0" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C83" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>-0.325%</t>
         </is>
@@ -3563,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -4419,145 +4149,10 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B59" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B60" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B61" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C61" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B62" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B63" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C63" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B64" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B65" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C65" s="0" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C66" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>-3.0281%</t>
         </is>
@@ -4574,7 +4169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5430,145 +5025,10 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" t="n">
         <v>0.99244</v>
       </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B59" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B60" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B61" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C61" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B62" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B63" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C63" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B64" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B65" s="0" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C65" s="0" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C66" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>-3.4901%</t>
         </is>
@@ -5586,7 +5046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5632,145 +5092,10 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" t="n">
         <v>1.00005</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5787,7 +5112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5833,145 +5158,10 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" t="n">
         <v>1.00005</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>0%</t>
         </is>

--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19031" windowHeight="6972" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="22095" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.00000_ "/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy\/mm\/dd"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy\/mm\/dd"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -630,7 +631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -641,9 +642,40 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -651,11 +683,15 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1033,1121 +1069,1626 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E70"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="6" min="2" max="2"/>
-    <col width="10.7777777777778" customWidth="1" style="7" min="3" max="3"/>
+    <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
+    <col width="16.375" customWidth="1" style="13" min="2" max="2"/>
+    <col width="15.25" customWidth="1" style="14" min="3" max="3"/>
+    <col width="15.875" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16.125" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9" customWidth="1" style="5" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="15" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="5" t="n">
         <v>0.99998</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>-0.002%</t>
         </is>
       </c>
+      <c r="D4" s="5" t="n">
+        <v>0.99998</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>-0.002%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="5" t="n">
         <v>1.00004</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.00004</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="5" t="n">
         <v>0.99956</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D7" s="5" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="5" t="n">
         <v>0.99956</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D8" s="5" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="5" t="n">
         <v>0.99956</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D9" s="5" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="5" t="n">
         <v>0.99986</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>-0.018%</t>
         </is>
       </c>
+      <c r="D10" s="5" t="n">
+        <v>0.99986</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>-0.018%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="5" t="n">
         <v>0.99958</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>-0.046%</t>
         </is>
       </c>
+      <c r="D11" s="5" t="n">
+        <v>0.99958</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-0.046%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="5" t="n">
         <v>0.99984</v>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D12" s="5" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="5" t="n">
         <v>0.99984</v>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D13" s="5" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="5" t="n">
         <v>0.9994</v>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>-0.064%</t>
         </is>
       </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-0.064%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="5" t="n">
         <v>0.99938</v>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>-0.066%</t>
         </is>
       </c>
+      <c r="D15" s="5" t="n">
+        <v>0.99938</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-0.066%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="5" t="n">
         <v>0.99905</v>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>-0.099%</t>
         </is>
       </c>
+      <c r="D16" s="5" t="n">
+        <v>0.99905</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-0.099%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="5" t="n">
         <v>0.99771</v>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>-0.233%</t>
         </is>
       </c>
+      <c r="D17" s="5" t="n">
+        <v>0.99771</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-0.233%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="5" t="n">
         <v>0.99775</v>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>-0.229%</t>
         </is>
       </c>
+      <c r="D18" s="5" t="n">
+        <v>0.99775</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-0.229%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="5" t="n">
         <v>0.99776</v>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>-0.228%</t>
         </is>
       </c>
+      <c r="D19" s="5" t="n">
+        <v>0.99776</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>-0.228%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="5" t="n">
         <v>0.9978</v>
       </c>
-      <c r="C20" s="0" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>-0.224%</t>
         </is>
       </c>
+      <c r="D20" s="5" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>-0.224%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="5" t="n">
         <v>0.99788</v>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>-0.216%</t>
         </is>
       </c>
+      <c r="D21" s="5" t="n">
+        <v>0.99788</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>-0.216%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="5" t="n">
         <v>0.99798</v>
       </c>
-      <c r="C22" s="0" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>-0.206%</t>
         </is>
       </c>
+      <c r="D22" s="5" t="n">
+        <v>0.99798</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>-0.206%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="5" t="n">
         <v>0.9980599999999999</v>
       </c>
-      <c r="C23" s="0" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>-0.198%</t>
         </is>
       </c>
+      <c r="D23" s="5" t="n">
+        <v>0.9980599999999999</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>-0.198%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="5" t="n">
         <v>0.99799</v>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>-0.205%</t>
         </is>
       </c>
+      <c r="D24" s="5" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>-0.205%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="5" t="n">
         <v>0.9981</v>
       </c>
-      <c r="C25" s="0" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>-0.194%</t>
         </is>
       </c>
+      <c r="D25" s="5" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>-0.194%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="5" t="n">
         <v>0.99813</v>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>-0.191%</t>
         </is>
       </c>
+      <c r="D26" s="5" t="n">
+        <v>0.99813</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>-0.191%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="5" t="n">
         <v>0.99825</v>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>-0.179%</t>
         </is>
       </c>
+      <c r="D27" s="5" t="n">
+        <v>0.99825</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>-0.179%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="5" t="n">
         <v>0.99829</v>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>-0.175%</t>
         </is>
       </c>
+      <c r="D28" s="5" t="n">
+        <v>0.99829</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>-0.175%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="5" t="n">
         <v>0.99873</v>
       </c>
-      <c r="C29" s="0" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>-0.131%</t>
         </is>
       </c>
+      <c r="D29" s="5" t="n">
+        <v>0.99873</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>-0.131%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="5" t="n">
         <v>0.99878</v>
       </c>
-      <c r="C30" s="0" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>-0.126%</t>
         </is>
       </c>
+      <c r="D30" s="5" t="n">
+        <v>0.99878</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>-0.126%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="5" t="n">
         <v>0.99913</v>
       </c>
-      <c r="C31" s="0" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>-0.091%</t>
         </is>
       </c>
+      <c r="D31" s="5" t="n">
+        <v>0.99913</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>-0.091%</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="5" t="n">
         <v>0.9952299999999999</v>
       </c>
-      <c r="C32" s="0" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>-0.481%</t>
         </is>
       </c>
+      <c r="D32" s="5" t="n">
+        <v>0.9952299999999999</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>-0.481%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="5" t="n">
         <v>0.99587</v>
       </c>
-      <c r="C33" s="0" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D33" s="5" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="5" t="n">
         <v>0.9958900000000001</v>
       </c>
-      <c r="C34" s="0" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>-0.415%</t>
         </is>
       </c>
+      <c r="D34" s="5" t="n">
+        <v>0.9958900000000001</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>-0.415%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="5" t="n">
         <v>0.99593</v>
       </c>
-      <c r="C35" s="0" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>-0.411%</t>
         </is>
       </c>
+      <c r="D35" s="5" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>-0.411%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="5" t="n">
         <v>0.99627</v>
       </c>
-      <c r="C36" s="0" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>-0.377%</t>
         </is>
       </c>
+      <c r="D36" s="5" t="n">
+        <v>0.99627</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>-0.377%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="5" t="n">
         <v>0.99875</v>
       </c>
-      <c r="C37" s="0" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>-0.129%</t>
         </is>
       </c>
+      <c r="D37" s="5" t="n">
+        <v>0.99875</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>-0.129%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="5" t="n">
         <v>0.9988</v>
       </c>
-      <c r="C38" s="0" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>-0.124%</t>
         </is>
       </c>
+      <c r="D38" s="5" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>-0.124%</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="5" t="n">
         <v>0.9988899999999999</v>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>-0.115%</t>
         </is>
       </c>
+      <c r="D39" s="5" t="n">
+        <v>0.9988899999999999</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>-0.115%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="5" t="n">
         <v>0.99826</v>
       </c>
-      <c r="C40" s="0" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>-0.178%</t>
         </is>
       </c>
+      <c r="D40" s="5" t="n">
+        <v>0.99826</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>-0.178%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="5" t="n">
         <v>0.9972299999999999</v>
       </c>
-      <c r="C41" s="0" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>-0.281%</t>
         </is>
       </c>
+      <c r="D41" s="5" t="n">
+        <v>0.9972299999999999</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>-0.281%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="5" t="n">
         <v>0.99742</v>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>-0.262%</t>
         </is>
       </c>
+      <c r="D42" s="5" t="n">
+        <v>0.99742</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>-0.262%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="5" t="n">
         <v>0.99747</v>
       </c>
-      <c r="C43" s="0" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>-0.257%</t>
         </is>
       </c>
+      <c r="D43" s="5" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="5" t="n">
         <v>0.9978399999999999</v>
       </c>
-      <c r="C44" s="0" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>-0.22%</t>
         </is>
       </c>
+      <c r="D44" s="5" t="n">
+        <v>0.9978399999999999</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="5" t="n">
         <v>0.99659</v>
       </c>
-      <c r="C45" s="0" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>-0.345%</t>
         </is>
       </c>
+      <c r="D45" s="5" t="n">
+        <v>0.99659</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>-0.345%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="5" t="n">
         <v>0.9956700000000001</v>
       </c>
-      <c r="C46" s="0" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>-0.437%</t>
         </is>
       </c>
+      <c r="D46" s="5" t="n">
+        <v>0.9956700000000001</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>-0.437%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="5" t="n">
         <v>0.99419</v>
       </c>
-      <c r="C47" s="0" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>-0.585%</t>
         </is>
       </c>
+      <c r="D47" s="5" t="n">
+        <v>0.99419</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>-0.585%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="5" t="n">
         <v>0.99431</v>
       </c>
-      <c r="C48" s="0" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>-0.573%</t>
         </is>
       </c>
+      <c r="D48" s="5" t="n">
+        <v>0.99431</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>-0.573%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="5" t="n">
         <v>0.99477</v>
       </c>
-      <c r="C49" s="0" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>-0.527%</t>
         </is>
       </c>
+      <c r="D49" s="5" t="n">
+        <v>0.99477</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>-0.527%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="5" t="n">
         <v>0.99587</v>
       </c>
-      <c r="C50" s="0" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D50" s="5" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="5" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C51" s="0" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>-0.325%</t>
         </is>
       </c>
+      <c r="D51" s="5" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="5" t="n">
         <v>0.99732</v>
       </c>
-      <c r="C52" s="0" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>-0.272%</t>
         </is>
       </c>
+      <c r="D52" s="5" t="n">
+        <v>0.99732</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>-0.272%</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="5" t="n">
         <v>0.99678</v>
       </c>
-      <c r="C53" s="0" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>-0.326%</t>
         </is>
       </c>
+      <c r="D53" s="5" t="n">
+        <v>0.99678</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>-0.326%</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="5" t="n">
         <v>0.99704</v>
       </c>
-      <c r="C54" s="0" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>-0.3%</t>
         </is>
       </c>
+      <c r="D54" s="5" t="n">
+        <v>0.99704</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="5" t="n">
         <v>0.99718</v>
       </c>
-      <c r="C55" s="0" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>-0.286%</t>
         </is>
       </c>
+      <c r="D55" s="5" t="n">
+        <v>0.99718</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>-0.286%</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="5" t="n">
         <v>0.99717</v>
       </c>
-      <c r="C56" s="0" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>-0.287%</t>
         </is>
       </c>
+      <c r="D56" s="5" t="n">
+        <v>0.99717</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>-0.287%</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="5" t="n">
         <v>0.99721</v>
       </c>
-      <c r="C57" s="0" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>-0.283%</t>
         </is>
       </c>
+      <c r="D57" s="5" t="n">
+        <v>0.99721</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>-0.283%</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="5" t="n">
         <v>0.9973</v>
       </c>
-      <c r="C58" s="0" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>-0.274%</t>
         </is>
       </c>
+      <c r="D58" s="5" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>-0.274%</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="5" t="n">
         <v>0.99747</v>
       </c>
-      <c r="C59" s="0" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>-0.257%</t>
         </is>
       </c>
+      <c r="D59" s="5" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="5" t="n">
         <v>0.99765</v>
       </c>
-      <c r="C60" s="0" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>-0.239%</t>
         </is>
       </c>
+      <c r="D60" s="5" t="n">
+        <v>0.99765</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>-0.239%</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="5" t="n">
         <v>0.99761</v>
       </c>
-      <c r="C61" s="0" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>-0.243%</t>
         </is>
       </c>
+      <c r="D61" s="5" t="n">
+        <v>0.99761</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>-0.243%</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="5" t="n">
         <v>0.99726</v>
       </c>
-      <c r="C62" s="0" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>-0.278%</t>
         </is>
       </c>
+      <c r="D62" s="5" t="n">
+        <v>0.99726</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>-0.278%</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="5" t="n">
         <v>0.99598</v>
       </c>
-      <c r="C63" s="0" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>-0.406%</t>
         </is>
       </c>
+      <c r="D63" s="5" t="n">
+        <v>0.99598</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>-0.406%</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="5" t="n">
         <v>0.9962</v>
       </c>
-      <c r="C64" s="0" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>-0.384%</t>
         </is>
       </c>
+      <c r="D64" s="5" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>-0.384%</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="5" t="n">
         <v>0.99654</v>
       </c>
-      <c r="C65" s="0" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>-0.35%</t>
         </is>
       </c>
+      <c r="D65" s="5" t="n">
+        <v>0.99654</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="5" t="n">
         <v>0.99668</v>
       </c>
-      <c r="C66" s="0" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>-0.336%</t>
         </is>
       </c>
+      <c r="D66" s="5" t="n">
+        <v>0.99668</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>-0.336%</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B67" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C67" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>-0.7027%</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>0.9930099999999999</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/30</t>
+      <c r="A68" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B68" s="0" t="n">
-        <v>0.99629</v>
+        <v>0.99679</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>-0.375%</t>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>0.9930099999999999</v>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>-0.7027%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B69" s="0" t="n">
-        <v>0.9966</v>
+        <v>0.99679</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>-0.344%</t>
+          <t>-0.7027%</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>0.9930099999999999</v>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="B70" s="0" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>-0.374%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/05</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>0.99649</v>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>-0.355%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/06</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>0.99654</v>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>-0.35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/09</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>0.99646</v>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>-0.358%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A70" s="23" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B70" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.9930099999999999</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-0.7027%</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2704,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E70"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="6" min="2" max="2"/>
-    <col width="10.7777777777778" customWidth="1" style="7" min="3" max="3"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2177,32 +2718,50 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="19" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -2215,9 +2774,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -2230,9 +2797,17 @@
           <t>-0.002%</t>
         </is>
       </c>
+      <c r="D4" s="0" t="n">
+        <v>0.99998</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>-0.002%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -2245,9 +2820,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -2260,9 +2843,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>1.00004</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -2275,9 +2866,17 @@
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -2290,9 +2889,17 @@
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -2305,9 +2912,17 @@
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -2320,9 +2935,17 @@
           <t>-0.018%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99986</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.018%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -2335,9 +2958,17 @@
           <t>-0.046%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99958</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.046%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -2350,9 +2981,17 @@
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -2365,9 +3004,17 @@
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -2380,9 +3027,17 @@
           <t>-0.064%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.064%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -2395,9 +3050,17 @@
           <t>-0.066%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99938</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.066%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -2410,9 +3073,17 @@
           <t>-0.099%</t>
         </is>
       </c>
+      <c r="D16" s="0" t="n">
+        <v>0.99905</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>-0.099%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -2425,9 +3096,17 @@
           <t>-0.233%</t>
         </is>
       </c>
+      <c r="D17" s="0" t="n">
+        <v>0.99771</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>-0.233%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -2440,9 +3119,17 @@
           <t>-0.229%</t>
         </is>
       </c>
+      <c r="D18" s="0" t="n">
+        <v>0.99775</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>-0.229%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -2455,9 +3142,17 @@
           <t>-0.228%</t>
         </is>
       </c>
+      <c r="D19" s="0" t="n">
+        <v>0.99776</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>-0.228%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -2470,9 +3165,17 @@
           <t>-0.224%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.224%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -2485,9 +3188,17 @@
           <t>-0.216%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>0.99788</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.216%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -2500,9 +3211,17 @@
           <t>-0.206%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99798</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.206%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -2515,9 +3234,17 @@
           <t>-0.198%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.9980599999999999</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.198%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -2530,9 +3257,17 @@
           <t>-0.205%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.205%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -2545,9 +3280,17 @@
           <t>-0.194%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.194%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -2560,9 +3303,17 @@
           <t>-0.191%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>0.99813</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.191%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -2575,9 +3326,17 @@
           <t>-0.179%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>0.99825</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.179%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -2590,9 +3349,17 @@
           <t>-0.175%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>0.99829</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.175%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -2605,9 +3372,17 @@
           <t>-0.131%</t>
         </is>
       </c>
+      <c r="D29" s="0" t="n">
+        <v>0.99873</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>-0.131%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -2620,9 +3395,17 @@
           <t>-0.126%</t>
         </is>
       </c>
+      <c r="D30" s="0" t="n">
+        <v>0.99878</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.126%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -2635,9 +3418,17 @@
           <t>-0.091%</t>
         </is>
       </c>
+      <c r="D31" s="0" t="n">
+        <v>0.99913</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>-0.091%</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -2650,9 +3441,17 @@
           <t>-0.481%</t>
         </is>
       </c>
+      <c r="D32" s="0" t="n">
+        <v>0.9952299999999999</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>-0.481%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -2665,9 +3464,17 @@
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D33" s="0" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -2680,9 +3487,17 @@
           <t>-0.391%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>0.99613</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.391%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -2695,9 +3510,17 @@
           <t>-0.387%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>0.99617</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.387%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -2710,9 +3533,17 @@
           <t>-0.354%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.354%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -2725,9 +3556,17 @@
           <t>-0.107%</t>
         </is>
       </c>
+      <c r="D37" s="0" t="n">
+        <v>0.99897</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>-0.107%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -2740,9 +3579,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D38" s="0" t="n">
+        <v>0.99899</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -2755,9 +3602,17 @@
           <t>-0.096%</t>
         </is>
       </c>
+      <c r="D39" s="0" t="n">
+        <v>0.99908</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>-0.096%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -2770,9 +3625,17 @@
           <t>-0.159%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>0.9984499999999999</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.159%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -2785,9 +3648,17 @@
           <t>-0.262%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>0.99742</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.262%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -2800,9 +3671,17 @@
           <t>-0.243%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>0.99761</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.243%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -2815,9 +3694,17 @@
           <t>-0.238%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>0.99766</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.238%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -2830,9 +3717,17 @@
           <t>-0.201%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>0.99803</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.201%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -2845,9 +3740,17 @@
           <t>-0.324%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.324%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -2860,9 +3763,17 @@
           <t>-0.419%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>0.99585</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-0.419%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -2875,9 +3786,17 @@
           <t>-0.566%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>0.99438</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-0.566%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -2890,9 +3809,17 @@
           <t>-0.553%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>0.99451</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-0.553%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -2905,9 +3832,17 @@
           <t>-0.527%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>0.99477</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-0.527%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -2920,9 +3855,17 @@
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D50" s="0" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -2935,9 +3878,17 @@
           <t>-0.325%</t>
         </is>
       </c>
+      <c r="D51" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -2950,9 +3901,17 @@
           <t>-0.272%</t>
         </is>
       </c>
+      <c r="D52" s="0" t="n">
+        <v>0.99732</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>-0.272%</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -2965,9 +3924,17 @@
           <t>-0.326%</t>
         </is>
       </c>
+      <c r="D53" s="0" t="n">
+        <v>0.99678</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>-0.326%</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -2980,9 +3947,17 @@
           <t>-0.3%</t>
         </is>
       </c>
+      <c r="D54" s="0" t="n">
+        <v>0.99704</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -2995,9 +3970,17 @@
           <t>-0.286%</t>
         </is>
       </c>
+      <c r="D55" s="0" t="n">
+        <v>0.99718</v>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>-0.286%</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -3010,9 +3993,17 @@
           <t>-0.287%</t>
         </is>
       </c>
+      <c r="D56" s="0" t="n">
+        <v>0.99717</v>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>-0.287%</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -3025,9 +4016,17 @@
           <t>-0.283%</t>
         </is>
       </c>
+      <c r="D57" s="0" t="n">
+        <v>0.99721</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>-0.283%</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -3040,9 +4039,17 @@
           <t>-0.274%</t>
         </is>
       </c>
+      <c r="D58" s="0" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>-0.274%</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -3055,9 +4062,17 @@
           <t>-0.257%</t>
         </is>
       </c>
+      <c r="D59" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -3070,9 +4085,17 @@
           <t>-0.239%</t>
         </is>
       </c>
+      <c r="D60" s="0" t="n">
+        <v>0.99765</v>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>-0.239%</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -3085,9 +4108,17 @@
           <t>-0.243%</t>
         </is>
       </c>
+      <c r="D61" s="0" t="n">
+        <v>0.99761</v>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>-0.243%</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -3100,9 +4131,17 @@
           <t>-0.278%</t>
         </is>
       </c>
+      <c r="D62" s="0" t="n">
+        <v>0.99726</v>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>-0.278%</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -3115,9 +4154,17 @@
           <t>-0.406%</t>
         </is>
       </c>
+      <c r="D63" s="0" t="n">
+        <v>0.99598</v>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>-0.406%</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -3130,9 +4177,17 @@
           <t>-0.384%</t>
         </is>
       </c>
+      <c r="D64" s="0" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>-0.384%</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -3145,9 +4200,17 @@
           <t>-0.35%</t>
         </is>
       </c>
+      <c r="D65" s="0" t="n">
+        <v>0.99654</v>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -3160,124 +4223,104 @@
           <t>-0.336%</t>
         </is>
       </c>
+      <c r="D66" s="0" t="n">
+        <v>0.99668</v>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>-0.336%</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B67" s="0" t="n">
-        <v>0.99661</v>
+        <v>0.99671</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>-0.343%</t>
+          <t>-0.6622%</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>0.99342</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/30</t>
+      <c r="A68" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B68" s="0" t="n">
-        <v>0.99629</v>
+        <v>0.99671</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>-0.375%</t>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>0.99342</v>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>-0.6622%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B69" s="0" t="n">
-        <v>0.9966</v>
+        <v>0.99671</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>-0.344%</t>
+          <t>-0.6622%</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>0.99342</v>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="B70" s="0" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>-0.374%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/05</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>0.99643</v>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>-0.361%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/06</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>0.99654</v>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>-0.35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/09</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>0.99652</v>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>-0.352%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A70" s="23" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>-0.325%</t>
+      <c r="B70" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.99342</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-0.6622%</t>
         </is>
       </c>
     </row>
@@ -3293,12 +4336,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="6" min="2" max="2"/>
-    <col width="10.7777777777778" customWidth="1" style="7" min="3" max="3"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3307,49 +4350,75 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -3362,9 +4431,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -3377,9 +4454,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -3392,9 +4477,17 @@
           <t>-0.113%</t>
         </is>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -3407,9 +4500,17 @@
           <t>-0.207%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -3422,9 +4523,17 @@
           <t>-0.271%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -3437,9 +4546,17 @@
           <t>-0.309%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -3452,9 +4569,17 @@
           <t>-0.457%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -3467,9 +4592,17 @@
           <t>-0.525%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -3482,9 +4615,17 @@
           <t>-0.502%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -3497,9 +4638,17 @@
           <t>-0.463%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -3512,9 +4661,17 @@
           <t>-0.781%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -3527,9 +4684,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -3542,9 +4707,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -3557,9 +4730,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00384</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -3572,9 +4753,17 @@
           <t>-0.0976%</t>
         </is>
       </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>-0.0976%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -3587,9 +4776,17 @@
           <t>-0.0249%</t>
         </is>
       </c>
+      <c r="D19" s="0" t="n">
+        <v>1.00359</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>-0.0249%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -3602,9 +4799,17 @@
           <t>-0.0508%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00333</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0508%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -3617,9 +4822,17 @@
           <t>-0.251%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00132</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.251%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -3632,9 +4845,17 @@
           <t>-0.4074%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99975</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4074%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -3647,9 +4868,17 @@
           <t>-0.4602%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.99922</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4602%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -3662,9 +4891,17 @@
           <t>-0.3267%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00056</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3267%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -3677,9 +4914,17 @@
           <t>-0.3228%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.3228%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -3692,9 +4937,17 @@
           <t>-0.2869%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>1.00096</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.2869%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -3707,9 +4960,17 @@
           <t>-0.4025%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.4025%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -3722,9 +4983,17 @@
           <t>-0.1833%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.1833%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -3737,9 +5006,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00457</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -3752,9 +5029,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00494</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -3767,9 +5052,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00596</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -3782,9 +5075,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00818</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -3797,9 +5098,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00916</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -3812,9 +5121,17 @@
           <t>-0.0466%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00869</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.0466%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -3827,9 +5144,17 @@
           <t>-0.1407%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00774</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.1407%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -3842,9 +5167,17 @@
           <t>-0.1516%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00763</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1516%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -3857,9 +5190,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01353</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -3872,9 +5213,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01567</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -3887,9 +5236,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02409</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -3902,9 +5259,17 @@
           <t>-0.0547%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02353</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.0547%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -3917,9 +5282,17 @@
           <t>-0.5273%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01869</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.5273%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -3932,9 +5305,17 @@
           <t>-0.7656%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01625</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.7656%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -3947,9 +5328,17 @@
           <t>-0.6972%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01695</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.6972%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -3962,9 +5351,17 @@
           <t>-0.4961%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01901</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.4961%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -3977,9 +5374,17 @@
           <t>-0.914%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01473</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.914%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -3992,9 +5397,17 @@
           <t>-1.412%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00963</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-1.412%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -4007,9 +5420,17 @@
           <t>-1.5311%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>1.00841</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.5311%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -4022,9 +5443,17 @@
           <t>-1.7655%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00601</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-1.7655%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -4037,124 +5466,104 @@
           <t>-1.744%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00623</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-1.744%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B50" s="0" t="n">
-        <v>1.00949</v>
+        <v>0.99308</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>-1.4257%</t>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/30</t>
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B51" s="0" t="n">
-        <v>1.00266</v>
+        <v>0.99308</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>-2.0926%</t>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B52" s="0" t="n">
-        <v>1.00131</v>
+        <v>0.99308</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>-2.2244%</t>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="B53" s="0" t="n">
-        <v>0.99663</v>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>-2.6814%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/05</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="n">
-        <v>0.99563</v>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>-2.7791%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/06</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="n">
-        <v>0.99381</v>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>-2.9568%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/09</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="n">
-        <v>0.9930600000000001</v>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>-3.03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B53" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>-3.0281%</t>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +5578,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="6" min="2" max="2"/>
-    <col width="10.7777777777778" customWidth="1" style="7" min="3" max="3"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4183,49 +5592,75 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -4238,9 +5673,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -4253,9 +5696,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -4268,9 +5719,17 @@
           <t>-0.113%</t>
         </is>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -4283,9 +5742,17 @@
           <t>-0.207%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -4298,9 +5765,17 @@
           <t>-0.271%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -4313,9 +5788,17 @@
           <t>-0.309%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -4328,9 +5811,17 @@
           <t>-0.457%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -4343,9 +5834,17 @@
           <t>-0.525%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -4358,9 +5857,17 @@
           <t>-0.502%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -4373,9 +5880,17 @@
           <t>-0.463%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -4388,9 +5903,17 @@
           <t>-0.781%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -4403,9 +5926,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -4418,9 +5949,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -4433,9 +5972,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00351</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -4448,9 +5995,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -4463,9 +6018,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D19" s="0" t="n">
+        <v>1.0042</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -4478,9 +6041,17 @@
           <t>-0.0946%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00325</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0946%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -4493,9 +6064,17 @@
           <t>-0.3734%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00045</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.3734%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -4508,9 +6087,17 @@
           <t>-0.4551%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99963</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4551%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -4523,9 +6110,17 @@
           <t>-0.4242%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.9999400000000001</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4242%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -4538,9 +6133,17 @@
           <t>-0.3455%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00073</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3455%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -4553,9 +6156,17 @@
           <t>-0.2729%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>1.00146</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.2729%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -4568,9 +6179,17 @@
           <t>-0.1892%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>1.0023</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.1892%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -4583,9 +6202,17 @@
           <t>-0.2599%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>1.00159</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.2599%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -4598,9 +6225,17 @@
           <t>-0.0239%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>1.00396</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.0239%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -4613,9 +6248,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00616</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -4628,9 +6271,17 @@
           <t>-0.0427%</t>
         </is>
       </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00573</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.0427%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -4643,9 +6294,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00707</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -4658,9 +6317,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00825</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -4673,9 +6340,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00923</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -4688,9 +6363,17 @@
           <t>-0.1199%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00802</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.1199%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -4703,9 +6386,17 @@
           <t>-0.2338%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00687</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.2338%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -4718,9 +6409,17 @@
           <t>-0.1367%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00785</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1367%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -4733,9 +6432,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01623</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -4748,9 +6455,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01723</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -4763,9 +6478,17 @@
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02833</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -4778,9 +6501,17 @@
           <t>-0.5679%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02249</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.5679%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -4793,9 +6524,17 @@
           <t>-1.1455%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01655</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-1.1455%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -4808,9 +6547,17 @@
           <t>-1.1164%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01685</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-1.1164%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -4823,9 +6570,17 @@
           <t>-1.2233%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01575</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-1.2233%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -4838,9 +6593,17 @@
           <t>-0.8733%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01935</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.8733%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -4853,9 +6616,17 @@
           <t>-1.3527%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01442</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-1.3527%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -4868,9 +6639,17 @@
           <t>-2.0081%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00768</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-2.0081%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -4883,9 +6662,17 @@
           <t>-1.8506%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.8506%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -4898,9 +6685,17 @@
           <t>-2.0538%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00721</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-2.0538%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -4913,124 +6708,31 @@
           <t>-2.1277%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00645</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-2.1277%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
+      <c r="A50" s="20" t="n"/>
       <c r="B50" s="0" t="n">
-        <v>1.01243</v>
+        <v>1.00315</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>-1.5462%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>2025/05/30</t>
-        </is>
-      </c>
-      <c r="B51" s="0" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>-2.4486%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="n">
-        <v>1.00002</v>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>-2.753%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="B53" s="0" t="n">
-        <v>0.99647</v>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>-3.0982%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/05</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="n">
-        <v>0.99546</v>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>-3.1964%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/06</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="n">
-        <v>0.99494</v>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>-3.247%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/09</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="n">
-        <v>0.9946</v>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>-3.2801%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.99244</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>-3.4901%</t>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>1.00249</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-2.5132%</t>
         </is>
       </c>
     </row>
@@ -5046,13 +6748,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
-  <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="6" min="2" max="2"/>
-    <col width="10.7777777777778" customWidth="1" style="7" min="3" max="3"/>
-  </cols>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -5060,44 +6757,1147 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/09</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>0.99988</v>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>-0.0124%</t>
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>2025/03/18</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>2025/03/19</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/20</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/21</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/24</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/25</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/26</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/27</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/31</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/02</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/03</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/07</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/09</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>1.00384</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00384</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>-0.0976%</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>-0.0976%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/11</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>1.00359</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>-0.0249%</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>1.00359</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>-0.0249%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/14</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>1.00333</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0508%</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00333</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0508%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/15</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>1.00132</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>-0.251%</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00132</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.251%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/16</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>0.99975</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4074%</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99975</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4074%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/17</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>0.99922</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4602%</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>0.99922</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4602%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>1.00056</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3267%</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00056</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3267%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/21</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>-0.3228%</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.3228%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/22</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>1.00096</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>-0.2869%</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>1.00096</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.2869%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/23</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>-0.4025%</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.4025%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/24</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>-0.1833%</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.1833%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/25</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>1.00457</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00457</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/28</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>1.00494</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00494</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/29</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>1.00596</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00596</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>1.00818</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00818</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/06</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1.00916</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00916</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/07</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>1.00869</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>-0.0466%</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00869</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.0466%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/08</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>1.00774</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>-0.1407%</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00774</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.1407%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/09</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>1.00763</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1516%</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00763</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1516%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/12</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>1.01353</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01353</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/13</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>1.01567</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01567</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/14</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>1.02409</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02409</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>1.02353</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>-0.0547%</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02353</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.0547%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/16</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>1.01869</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>-0.5273%</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01869</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.5273%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/19</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>1.01625</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>-0.7656%</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01625</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.7656%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/20</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>1.01695</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>-0.6972%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01695</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.6972%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>1.01901</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-0.4961%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01901</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.4961%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/22</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>1.01473</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-0.914%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01473</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.914%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>1.00963</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>-1.412%</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00963</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-1.412%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>1.00841</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>-1.5311%</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>1.00841</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.5311%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/27</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>1.00601</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>-1.7655%</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00601</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-1.7655%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>1.00623</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>-1.744%</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00623</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-1.744%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="n"/>
+      <c r="B50" s="0" t="n">
         <v>1.00005</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>-2.3476%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>0.99805</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-2.5429%</t>
         </is>
       </c>
     </row>
@@ -5112,12 +7912,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="6" min="2" max="2"/>
-    <col width="10.7777777777778" customWidth="1" style="7" min="3" max="3"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5126,44 +7926,1147 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/09</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>0.99988</v>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>-0.0124%</t>
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>2025/03/18</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.00005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>2025/03/19</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/20</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/21</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/24</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/25</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/26</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/27</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>2025/03/31</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/02</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/03</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/07</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/09</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>1.00351</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00351</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/11</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>1.0042</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>1.0042</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/14</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>1.00325</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0946%</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00325</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0946%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/15</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>1.00045</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>-0.3734%</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00045</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.3734%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/16</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>0.99963</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4551%</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99963</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4551%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/17</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>0.9999400000000001</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4242%</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>0.9999400000000001</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4242%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>1.00073</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3455%</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00073</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3455%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/21</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>1.00146</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>-0.2729%</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>1.00146</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.2729%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/22</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>1.0023</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>-0.1892%</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>1.0023</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.1892%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/23</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>1.00159</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>-0.2599%</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>1.00159</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.2599%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/24</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>1.00396</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>-0.0239%</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>1.00396</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.0239%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/25</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>1.00616</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00616</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/28</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>1.00573</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>-0.0427%</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00573</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.0427%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/29</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>1.00707</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00707</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>1.00825</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00825</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/06</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1.00923</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00923</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/07</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>1.00802</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>-0.1199%</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00802</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.1199%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/08</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>1.00687</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>-0.2338%</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00687</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.2338%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/09</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>1.00785</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1367%</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00785</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1367%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/12</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>1.01623</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01623</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/13</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>1.01723</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01723</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/14</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>1.02833</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02833</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>1.02249</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>-0.5679%</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02249</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.5679%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/16</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>1.01655</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>-1.1455%</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01655</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-1.1455%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/19</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>1.01685</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>-1.1164%</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01685</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-1.1164%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/20</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>1.01575</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>-1.2233%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01575</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-1.2233%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>1.01935</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-0.8733%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01935</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.8733%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/22</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>1.01442</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-1.3527%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01442</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-1.3527%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>1.00768</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>-2.0081%</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00768</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-2.0081%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>-1.8506%</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.8506%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/27</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>1.00721</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>-2.0538%</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00721</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-2.0538%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>1.00645</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>-2.1277%</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00645</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-2.1277%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="n"/>
+      <c r="B50" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>-2.7485%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-2.9429%</t>
         </is>
       </c>
     </row>

--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>-0.7027%</t>
+          <t>-0.3251%</t>
         </is>
       </c>
       <c r="D67" s="0" t="n">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>-0.3251%</t>
+          <t>-0.7027%</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>-0.3251%</t>
+          <t>-0.7027%</t>
         </is>
       </c>
       <c r="D68" s="0" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>-0.7027%</t>
+          <t>-0.3251%</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>-0.7027%</t>
+          <t>-0.3251%</t>
         </is>
       </c>
       <c r="D69" s="0" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
-          <t>-0.3251%</t>
+          <t>-0.7027%</t>
         </is>
       </c>
     </row>
@@ -2675,18 +2675,41 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="0" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>-0.7027%</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>0.9930099999999999</v>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
         <is>
           <t>-0.3251%</t>
         </is>
       </c>
-      <c r="D70" t="n">
+    </row>
+    <row r="71">
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>0.9930099999999999</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>-0.7027%</t>
         </is>
@@ -2704,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4243,7 +4266,7 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>-0.6622%</t>
+          <t>-0.3334%</t>
         </is>
       </c>
       <c r="D67" s="0" t="n">
@@ -4251,7 +4274,7 @@
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>-0.3334%</t>
+          <t>-0.6622%</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4289,7 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>-0.3334%</t>
+          <t>-0.6622%</t>
         </is>
       </c>
       <c r="D68" s="0" t="n">
@@ -4274,7 +4297,7 @@
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>-0.6622%</t>
+          <t>-0.3334%</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4312,7 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>-0.6622%</t>
+          <t>-0.3334%</t>
         </is>
       </c>
       <c r="D69" s="0" t="n">
@@ -4297,7 +4320,7 @@
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
-          <t>-0.3334%</t>
+          <t>-0.6622%</t>
         </is>
       </c>
     </row>
@@ -4307,18 +4330,41 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="0" t="n">
         <v>0.99671</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>-0.6622%</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>0.99342</v>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
         <is>
           <t>-0.3334%</t>
         </is>
       </c>
-      <c r="D70" t="n">
+    </row>
+    <row r="71">
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>0.99342</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>-0.6622%</t>
         </is>
@@ -4336,7 +4382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -5486,7 +5532,7 @@
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>-3.0935%</t>
+          <t>-3.0284%</t>
         </is>
       </c>
       <c r="D50" s="0" t="n">
@@ -5494,7 +5540,7 @@
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>-3.0284%</t>
+          <t>-3.0935%</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5555,7 @@
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>-3.0284%</t>
+          <t>-3.0935%</t>
         </is>
       </c>
       <c r="D51" s="0" t="n">
@@ -5517,7 +5563,7 @@
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>-3.0935%</t>
+          <t>-3.0284%</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5578,7 @@
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>-3.0935%</t>
+          <t>-3.0284%</t>
         </is>
       </c>
       <c r="D52" s="0" t="n">
@@ -5540,7 +5586,7 @@
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>-3.0284%</t>
+          <t>-3.0935%</t>
         </is>
       </c>
     </row>
@@ -5550,18 +5596,41 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="0" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>-3.0284%</t>
         </is>
       </c>
-      <c r="D53" t="n">
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>0.99241</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>-3.0935%</t>
         </is>

--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
@@ -2790,20 +2790,158 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="0" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>-0.3251%</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0.9932</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="0" t="inlineStr">
         <is>
           <t>-0.6835%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>-0.6835%</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>-0.6835%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-0.6835%</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>0.99319</v>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>-0.6854%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-0.6854%</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>0.99319</v>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.99319</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-0.6854%</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4537,20 +4675,158 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="0" t="n">
         <v>0.99671</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>-0.3334%</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0.99312</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="0" t="inlineStr">
         <is>
           <t>-0.6919%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>-0.6919%</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>0.99312</v>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>0.99312</v>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>-0.6919%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-0.6919%</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>0.99312</v>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>-0.6937%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-0.6937%</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-0.6937%</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -5895,20 +6171,158 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="0" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>-3.0284%</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>0.99241</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="0" t="inlineStr">
         <is>
           <t>-3.0935%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>-3.0978%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>-3.0978%</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-3.0978%</t>
         </is>
       </c>
     </row>
@@ -7073,11 +7487,11 @@
         </is>
       </c>
       <c r="D50" s="0" t="n">
-        <v>1.00249</v>
+        <v>1.00244</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>-2.5132%</t>
+          <t>-2.5176%</t>
         </is>
       </c>
     </row>
@@ -8238,11 +8652,11 @@
         </is>
       </c>
       <c r="D50" s="0" t="n">
-        <v>0.99805</v>
+        <v>0.99798</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>-2.5429%</t>
+          <t>-2.5494%</t>
         </is>
       </c>
     </row>
@@ -9407,11 +9821,11 @@
         </is>
       </c>
       <c r="D50" s="0" t="n">
-        <v>0.99807</v>
+        <v>0.998</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>-2.9429%</t>
+          <t>-2.9494%</t>
         </is>
       </c>
     </row>

--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
@@ -2698,20 +2698,112 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="0" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>-0.3251%</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0.9930099999999999</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t>-0.7027%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>-0.6835%</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>-0.6835%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>-0.6835%</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-0.6835%</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4353,20 +4445,112 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="0" t="n">
         <v>0.99671</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>-0.3334%</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0.99342</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t>-0.6622%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>-0.6919%</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>0.99312</v>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>0.99312</v>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>-0.6919%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>-0.6919%</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>0.99312</v>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.99312</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-0.6919%</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -5619,18 +5803,110 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="0" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>-3.0284%</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>0.99241</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>-3.0935%</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.99241</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>-3.0935%</t>
         </is>

--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -677,6 +677,9 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -687,11 +690,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
@@ -2601,7 +2601,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="inlineStr">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -2611,20 +2611,20 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
+          <t>-0.6854%</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>0.99319</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
           <t>-0.3251%</t>
         </is>
       </c>
-      <c r="D67" s="0" t="n">
-        <v>0.9930099999999999</v>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
-        <is>
-          <t>-0.7027%</t>
-        </is>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" s="23" t="inlineStr">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -2634,20 +2634,20 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>-0.7027%</t>
+          <t>-0.3251%</t>
         </is>
       </c>
       <c r="D68" s="0" t="n">
-        <v>0.9930099999999999</v>
+        <v>0.99319</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>-0.3251%</t>
+          <t>-0.6854%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="23" t="inlineStr">
+      <c r="A69" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -2657,289 +2657,36 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
+          <t>-0.6854%</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>0.99319</v>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
           <t>-0.3251%</t>
         </is>
       </c>
-      <c r="D69" s="0" t="n">
-        <v>0.9930099999999999</v>
-      </c>
-      <c r="E69" s="0" t="inlineStr">
-        <is>
-          <t>-0.7027%</t>
-        </is>
-      </c>
     </row>
     <row r="70">
-      <c r="A70" s="23" t="inlineStr">
+      <c r="A70" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>-0.7027%</t>
-        </is>
-      </c>
-      <c r="D70" s="0" t="n">
-        <v>0.9930099999999999</v>
-      </c>
-      <c r="E70" s="0" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>-0.3251%</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-      <c r="D71" s="0" t="n">
-        <v>0.9930099999999999</v>
-      </c>
-      <c r="E71" s="0" t="inlineStr">
-        <is>
-          <t>-0.7027%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>-0.6835%</t>
-        </is>
-      </c>
-      <c r="D72" s="0" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E72" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-      <c r="D73" s="0" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E73" s="0" t="inlineStr">
-        <is>
-          <t>-0.6835%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>-0.6835%</t>
-        </is>
-      </c>
-      <c r="D74" s="0" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E74" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E75" s="0" t="inlineStr">
-        <is>
-          <t>-0.6835%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t>-0.6835%</t>
-        </is>
-      </c>
-      <c r="D76" s="0" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E76" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-      <c r="D77" s="0" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E77" s="0" t="inlineStr">
-        <is>
-          <t>-0.6835%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C78" s="0" t="inlineStr">
-        <is>
-          <t>-0.6835%</t>
-        </is>
-      </c>
-      <c r="D78" s="0" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E78" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C79" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-      <c r="D79" s="0" t="n">
+      <c r="D70" t="n">
         <v>0.99319</v>
       </c>
-      <c r="E79" s="0" t="inlineStr">
-        <is>
-          <t>-0.6854%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t>-0.6854%</t>
-        </is>
-      </c>
-      <c r="D80" s="0" t="n">
-        <v>0.99319</v>
-      </c>
-      <c r="E80" s="0" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>-0.3251%</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0.99319</v>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>-0.6854%</t>
         </is>
@@ -2957,12 +2704,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2993,28 +2740,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="n">
+      <c r="A2" s="20" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -3037,7 +2784,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -3060,7 +2807,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -3083,7 +2830,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -3106,7 +2853,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -3129,7 +2876,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -3152,7 +2899,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -3175,7 +2922,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -3198,7 +2945,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -3221,7 +2968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -3244,7 +2991,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -3267,7 +3014,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -3290,7 +3037,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -3313,7 +3060,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -3336,7 +3083,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -3359,7 +3106,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -3382,7 +3129,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -3405,7 +3152,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -3428,7 +3175,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -3451,7 +3198,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -3474,7 +3221,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -3497,7 +3244,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -3520,7 +3267,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -3543,7 +3290,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -3566,7 +3313,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -3589,7 +3336,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -3612,7 +3359,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -3635,7 +3382,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -3658,7 +3405,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -3681,7 +3428,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -3704,7 +3451,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -3727,7 +3474,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -3750,7 +3497,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -3773,7 +3520,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -3796,7 +3543,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -3819,7 +3566,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -3842,7 +3589,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -3865,7 +3612,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -3888,7 +3635,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -3911,7 +3658,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -3934,7 +3681,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -3957,7 +3704,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -3980,7 +3727,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -4003,7 +3750,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -4026,7 +3773,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -4049,7 +3796,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -4072,7 +3819,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -4095,7 +3842,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -4118,7 +3865,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -4141,7 +3888,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -4164,7 +3911,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -4187,7 +3934,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -4210,7 +3957,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -4233,7 +3980,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -4256,7 +4003,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -4279,7 +4026,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -4302,7 +4049,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="20" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -4325,7 +4072,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -4348,7 +4095,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -4371,7 +4118,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -4394,7 +4141,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -4417,7 +4164,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -4440,7 +4187,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="20" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -4463,7 +4210,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -4486,7 +4233,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="23" t="inlineStr">
+      <c r="A67" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -4496,20 +4243,20 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
+          <t>-0.6937%</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
           <t>-0.3334%</t>
         </is>
       </c>
-      <c r="D67" s="0" t="n">
-        <v>0.99342</v>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
-        <is>
-          <t>-0.6622%</t>
-        </is>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" s="23" t="inlineStr">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -4519,20 +4266,20 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>-0.6622%</t>
+          <t>-0.3334%</t>
         </is>
       </c>
       <c r="D68" s="0" t="n">
-        <v>0.99342</v>
+        <v>0.9931</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>-0.3334%</t>
+          <t>-0.6937%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="23" t="inlineStr">
+      <c r="A69" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -4542,289 +4289,36 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
+          <t>-0.6937%</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
           <t>-0.3334%</t>
         </is>
       </c>
-      <c r="D69" s="0" t="n">
-        <v>0.99342</v>
-      </c>
-      <c r="E69" s="0" t="inlineStr">
-        <is>
-          <t>-0.6622%</t>
-        </is>
-      </c>
     </row>
     <row r="70">
-      <c r="A70" s="23" t="inlineStr">
+      <c r="A70" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" t="n">
         <v>0.99671</v>
       </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>-0.6622%</t>
-        </is>
-      </c>
-      <c r="D70" s="0" t="n">
-        <v>0.99342</v>
-      </c>
-      <c r="E70" s="0" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>-0.3334%</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-      <c r="D71" s="0" t="n">
-        <v>0.99342</v>
-      </c>
-      <c r="E71" s="0" t="inlineStr">
-        <is>
-          <t>-0.6622%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>-0.6919%</t>
-        </is>
-      </c>
-      <c r="D72" s="0" t="n">
-        <v>0.99312</v>
-      </c>
-      <c r="E72" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-      <c r="D73" s="0" t="n">
-        <v>0.99312</v>
-      </c>
-      <c r="E73" s="0" t="inlineStr">
-        <is>
-          <t>-0.6919%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>-0.6919%</t>
-        </is>
-      </c>
-      <c r="D74" s="0" t="n">
-        <v>0.99312</v>
-      </c>
-      <c r="E74" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="n">
-        <v>0.99312</v>
-      </c>
-      <c r="E75" s="0" t="inlineStr">
-        <is>
-          <t>-0.6919%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t>-0.6919%</t>
-        </is>
-      </c>
-      <c r="D76" s="0" t="n">
-        <v>0.99312</v>
-      </c>
-      <c r="E76" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-      <c r="D77" s="0" t="n">
-        <v>0.99312</v>
-      </c>
-      <c r="E77" s="0" t="inlineStr">
-        <is>
-          <t>-0.6919%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C78" s="0" t="inlineStr">
-        <is>
-          <t>-0.6919%</t>
-        </is>
-      </c>
-      <c r="D78" s="0" t="n">
-        <v>0.99312</v>
-      </c>
-      <c r="E78" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C79" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-      <c r="D79" s="0" t="n">
+      <c r="D70" t="n">
         <v>0.9931</v>
       </c>
-      <c r="E79" s="0" t="inlineStr">
-        <is>
-          <t>-0.6937%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t>-0.6937%</t>
-        </is>
-      </c>
-      <c r="D80" s="0" t="n">
-        <v>0.9931</v>
-      </c>
-      <c r="E80" s="0" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.99671</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>-0.3334%</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0.9931</v>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>-0.6937%</t>
         </is>
@@ -4842,12 +4336,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4878,53 +4372,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="n">
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -4947,7 +4441,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -4970,7 +4464,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -4993,7 +4487,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -5016,7 +4510,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -5039,7 +4533,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -5062,7 +4556,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -5085,7 +4579,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -5108,7 +4602,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -5131,7 +4625,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -5154,7 +4648,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -5177,7 +4671,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -5200,7 +4694,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -5223,7 +4717,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -5246,7 +4740,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -5269,7 +4763,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -5292,7 +4786,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -5315,7 +4809,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -5338,7 +4832,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -5361,7 +4855,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -5384,7 +4878,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -5407,7 +4901,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -5430,7 +4924,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -5453,7 +4947,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -5476,7 +4970,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -5499,7 +4993,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -5522,7 +5016,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -5545,7 +5039,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -5568,7 +5062,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -5591,7 +5085,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -5614,7 +5108,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -5637,7 +5131,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -5660,7 +5154,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -5683,7 +5177,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -5706,7 +5200,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -5729,7 +5223,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -5752,7 +5246,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -5775,7 +5269,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -5798,7 +5292,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -5821,7 +5315,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -5844,7 +5338,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -5867,7 +5361,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -5890,7 +5384,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -5913,7 +5407,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -5936,7 +5430,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -5959,7 +5453,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -5982,7 +5476,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -5992,20 +5486,20 @@
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
+          <t>-3.0978%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
           <t>-3.0284%</t>
         </is>
       </c>
-      <c r="D50" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -6015,20 +5509,20 @@
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>-3.0935%</t>
+          <t>-3.0284%</t>
         </is>
       </c>
       <c r="D51" s="0" t="n">
-        <v>0.99241</v>
+        <v>0.99237</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>-3.0284%</t>
+          <t>-3.0978%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -6038,289 +5532,36 @@
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
+          <t>-3.0978%</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
           <t>-3.0284%</t>
         </is>
       </c>
-      <c r="D52" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E52" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-      <c r="D53" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E53" s="0" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>-3.0284%</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-      <c r="D54" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-      <c r="D55" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-      <c r="D56" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E56" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B57" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-      <c r="D57" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E57" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-      <c r="D58" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E58" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B59" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-      <c r="D59" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E59" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B60" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-      <c r="D60" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E60" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B61" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C61" s="0" t="inlineStr">
-        <is>
-          <t>-3.0935%</t>
-        </is>
-      </c>
-      <c r="D61" s="0" t="n">
-        <v>0.99241</v>
-      </c>
-      <c r="E61" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B62" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-      <c r="D62" s="0" t="n">
+      <c r="D53" t="n">
         <v>0.99237</v>
       </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t>-3.0978%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B63" s="0" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C63" s="0" t="inlineStr">
-        <is>
-          <t>-3.0978%</t>
-        </is>
-      </c>
-      <c r="D63" s="0" t="n">
-        <v>0.99237</v>
-      </c>
-      <c r="E63" s="0" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="23" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>-3.0284%</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0.99237</v>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>-3.0978%</t>
         </is>
@@ -6341,8 +5582,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6373,53 +5614,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="n">
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -6442,7 +5683,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -6465,7 +5706,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -6488,7 +5729,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -6511,7 +5752,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -6534,7 +5775,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -6557,7 +5798,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -6580,7 +5821,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -6603,7 +5844,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -6626,7 +5867,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -6649,7 +5890,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -6672,7 +5913,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -6695,7 +5936,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -6718,7 +5959,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -6741,7 +5982,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -6764,7 +6005,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -6787,7 +6028,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -6810,7 +6051,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -6833,7 +6074,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -6856,7 +6097,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -6879,7 +6120,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -6902,7 +6143,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -6925,7 +6166,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -6948,7 +6189,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -6971,7 +6212,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -6994,7 +6235,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -7017,7 +6258,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -7040,7 +6281,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -7063,7 +6304,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -7086,7 +6327,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -7109,7 +6350,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -7132,7 +6373,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -7155,7 +6396,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -7178,7 +6419,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -7201,7 +6442,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -7224,7 +6465,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -7247,7 +6488,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -7270,7 +6511,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -7293,7 +6534,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -7316,7 +6557,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -7339,7 +6580,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -7362,7 +6603,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -7385,7 +6626,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -7408,7 +6649,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -7431,7 +6672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -7454,7 +6695,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -7477,7 +6718,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n"/>
+      <c r="A50" s="21" t="n"/>
       <c r="B50" s="0" t="n">
         <v>1.00315</v>
       </c>
@@ -7538,53 +6779,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="n">
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -7607,7 +6848,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -7630,7 +6871,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -7653,7 +6894,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -7676,7 +6917,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -7699,7 +6940,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -7722,7 +6963,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -7745,7 +6986,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -7768,7 +7009,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -7791,7 +7032,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -7814,7 +7055,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -7837,7 +7078,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -7860,7 +7101,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -7883,7 +7124,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -7906,7 +7147,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -7929,7 +7170,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -7952,7 +7193,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -7975,7 +7216,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -7998,7 +7239,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -8021,7 +7262,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -8044,7 +7285,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -8067,7 +7308,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -8090,7 +7331,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -8113,7 +7354,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -8136,7 +7377,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -8159,7 +7400,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -8182,7 +7423,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -8205,7 +7446,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -8228,7 +7469,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -8251,7 +7492,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -8274,7 +7515,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -8297,7 +7538,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -8320,7 +7561,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -8343,7 +7584,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -8366,7 +7607,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -8389,7 +7630,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -8412,7 +7653,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -8435,7 +7676,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -8458,7 +7699,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -8481,7 +7722,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -8504,7 +7745,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -8527,7 +7768,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -8550,7 +7791,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -8573,7 +7814,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -8596,7 +7837,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -8619,7 +7860,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -8642,7 +7883,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n"/>
+      <c r="A50" s="21" t="n"/>
       <c r="B50" s="0" t="n">
         <v>1.00005</v>
       </c>
@@ -8675,8 +7916,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8707,53 +7948,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="n">
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -8776,7 +8017,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -8799,7 +8040,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -8822,7 +8063,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -8845,7 +8086,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -8868,7 +8109,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -8891,7 +8132,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -8914,7 +8155,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -8937,7 +8178,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -8960,7 +8201,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -8983,7 +8224,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -9006,7 +8247,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -9029,7 +8270,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -9052,7 +8293,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -9075,7 +8316,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -9098,7 +8339,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -9121,7 +8362,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -9144,7 +8385,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -9167,7 +8408,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -9190,7 +8431,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -9213,7 +8454,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -9236,7 +8477,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -9259,7 +8500,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -9282,7 +8523,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -9305,7 +8546,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -9328,7 +8569,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -9351,7 +8592,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -9374,7 +8615,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -9397,7 +8638,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -9420,7 +8661,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -9443,7 +8684,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -9466,7 +8707,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -9489,7 +8730,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -9512,7 +8753,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -9535,7 +8776,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -9558,7 +8799,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -9581,7 +8822,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -9604,7 +8845,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -9627,7 +8868,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -9650,7 +8891,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -9673,7 +8914,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -9696,7 +8937,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -9719,7 +8960,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -9742,7 +8983,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -9765,7 +9006,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -9788,7 +9029,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -9811,7 +9052,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n"/>
+      <c r="A50" s="21" t="n"/>
       <c r="B50" s="0" t="n">
         <v>1.00007</v>
       </c>

--- a/template/6.12/净值.xlsx
+++ b/template/6.12/净值.xlsx
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
@@ -2675,18 +2675,41 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="0" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>-0.3251%</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0.99319</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>-0.6854%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>-0.3251%</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.99319</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>-0.6854%</t>
         </is>
@@ -2704,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4307,18 +4330,41 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="0" t="n">
         <v>0.99671</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>-0.3334%</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0.9931</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>-0.6937%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>-0.3334%</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>-0.6937%</t>
         </is>
@@ -4336,7 +4382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -5550,18 +5596,41 @@
           <t>2025/06/10</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="0" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>-3.0284%</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>0.99237</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>-3.0978%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>-3.0284%</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>-3.0978%</t>
         </is>
@@ -6718,7 +6787,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
       <c r="B50" s="0" t="n">
         <v>1.00315</v>
       </c>
@@ -7883,7 +7956,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
       <c r="B50" s="0" t="n">
         <v>1.00005</v>
       </c>
@@ -9052,7 +9129,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
       <c r="B50" s="0" t="n">
         <v>1.00007</v>
       </c>
